--- a/data/human_baseline_annotations/annotation_annotator3.xlsx
+++ b/data/human_baseline_annotations/annotation_annotator3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/railey/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6798CC-5E59-2441-A45F-BFB7B6AB2D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2F4D1C-03C0-574A-B2F1-BA8AF21FB710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18260" yWindow="1700" windowWidth="16240" windowHeight="17580" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18260" yWindow="1700" windowWidth="16240" windowHeight="17580" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9103" uniqueCount="4926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9103" uniqueCount="4925">
   <si>
     <t>PACUTE-Bench Human Baseline — Annotator 3</t>
   </si>
@@ -15563,12 +15563,6 @@
     <t>p I y I k</t>
   </si>
   <si>
-    <t>alii--iip</t>
-  </si>
-  <si>
-    <t>aoigangi</t>
-  </si>
-  <si>
     <t>kayá</t>
   </si>
   <si>
@@ -15612,6 +15606,9 @@
   </si>
   <si>
     <t>anasisa</t>
+  </si>
+  <si>
+    <t>mataon</t>
   </si>
 </sst>
 </file>
@@ -17027,7 +17024,7 @@
         <v>2239</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>2239</v>
+        <v>4924</v>
       </c>
       <c r="I12" s="9"/>
     </row>
@@ -20048,7 +20045,7 @@
         <v>2369</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>4914</v>
+        <v>4912</v>
       </c>
       <c r="I18" s="9"/>
     </row>
@@ -20075,7 +20072,7 @@
         <v>2411</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>4915</v>
+        <v>4913</v>
       </c>
       <c r="I19" s="9"/>
     </row>
@@ -20102,7 +20099,7 @@
         <v>2705</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>4916</v>
+        <v>4914</v>
       </c>
       <c r="I20" s="9"/>
     </row>
@@ -20318,7 +20315,7 @@
         <v>2735</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>4917</v>
+        <v>4915</v>
       </c>
       <c r="I28" s="9"/>
     </row>
@@ -20426,7 +20423,7 @@
         <v>2750</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>4918</v>
+        <v>4916</v>
       </c>
       <c r="I32" s="9"/>
     </row>
@@ -20696,7 +20693,7 @@
         <v>2790</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>4919</v>
+        <v>4917</v>
       </c>
       <c r="I42" s="9"/>
     </row>
@@ -20723,7 +20720,7 @@
         <v>2794</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>4920</v>
+        <v>4918</v>
       </c>
       <c r="I43" s="9"/>
     </row>
@@ -20750,7 +20747,7 @@
         <v>2798</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>4921</v>
+        <v>4919</v>
       </c>
       <c r="I44" s="9"/>
     </row>
@@ -20777,7 +20774,7 @@
         <v>2802</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>4922</v>
+        <v>4920</v>
       </c>
       <c r="I45" s="9"/>
     </row>
@@ -20804,7 +20801,7 @@
         <v>2806</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>4923</v>
+        <v>4921</v>
       </c>
       <c r="I46" s="9"/>
     </row>
@@ -20831,7 +20828,7 @@
         <v>2810</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>4924</v>
+        <v>4922</v>
       </c>
       <c r="I47" s="9"/>
     </row>
@@ -20939,7 +20936,7 @@
         <v>2825</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>4925</v>
+        <v>4923</v>
       </c>
       <c r="I51" s="9"/>
     </row>
@@ -42943,8 +42940,7 @@
   <cols>
     <col min="1" max="3" width="20.83203125" customWidth="1"/>
     <col min="4" max="6" width="40.83203125" style="11" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+    <col min="7" max="8" width="20.83203125" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
   </cols>
   <sheetData>
@@ -43621,7 +43617,7 @@
         <v>1314</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>4909</v>
+        <v>1314</v>
       </c>
       <c r="I25" s="9"/>
     </row>
@@ -44458,7 +44454,7 @@
         <v>1438</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>4910</v>
+        <v>1438</v>
       </c>
       <c r="I56" s="9"/>
     </row>
@@ -46154,7 +46150,7 @@
         <v>1568</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>4911</v>
+        <v>4909</v>
       </c>
       <c r="I7" s="3"/>
     </row>
@@ -48290,7 +48286,7 @@
         <v>1712</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>4912</v>
+        <v>4910</v>
       </c>
       <c r="I4" s="9"/>
     </row>
@@ -49100,7 +49096,7 @@
         <v>2059</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>4913</v>
+        <v>4911</v>
       </c>
       <c r="I34" s="9"/>
     </row>

--- a/data/human_baseline_annotations/annotation_annotator3.xlsx
+++ b/data/human_baseline_annotations/annotation_annotator3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/railey/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/railey/Documents/pacute/pacute-bench/data/human_baseline_annotations/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2F4D1C-03C0-574A-B2F1-BA8AF21FB710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18260" yWindow="1700" windowWidth="16240" windowHeight="17580" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
